--- a/data/raw/sales/Week 25/Tonor/Vendor Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 25/Tonor/Vendor Sales (SP-API).xlsx
@@ -1401,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
